--- a/Config/Excel/GameConfig/MonsterUnitConfig.xlsx
+++ b/Config/Excel/GameConfig/MonsterUnitConfig.xlsx
@@ -710,13 +710,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I4" t="n">
         <v>2.5</v>
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="G5" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I5" t="n">
         <v>3</v>
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="G6" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="H6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="I6" t="n">
         <v>2</v>
@@ -863,13 +863,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>250</v>
+        <v>220</v>
       </c>
       <c r="G7" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="H7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I7" t="n">
         <v>4</v>
@@ -914,13 +914,13 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="G8" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="H8" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="I8" t="n">
         <v>1.5</v>
@@ -965,13 +965,13 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>5000</v>
+        <v>3200</v>
       </c>
       <c r="G9" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="H9" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
